--- a/sample_nurses3.xlsx
+++ b/sample_nurses3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\정영록\Desktop\Jupyter\실험공방\듀티표작성프로그램\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89927FE8-2541-477B-8067-9F9325D3DBFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{659393CE-9762-4E18-855D-595EA1CA8765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="79">
   <si>
     <t>이름</t>
   </si>
@@ -157,9 +157,6 @@
     <t>서지영</t>
   </si>
   <si>
-    <t>임수현</t>
-  </si>
-  <si>
     <t>전나연</t>
   </si>
   <si>
@@ -167,9 +164,6 @@
   </si>
   <si>
     <t>중간연차</t>
-  </si>
-  <si>
-    <t>남소희</t>
   </si>
   <si>
     <t>문혜리</t>
@@ -254,15 +248,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>N</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>6D</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>O</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EDU</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -610,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ35"/>
+  <dimension ref="A1:AJ33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.3">
@@ -754,6 +752,9 @@
       <c r="B5" t="s">
         <v>41</v>
       </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -762,6 +763,12 @@
       <c r="B6" t="s">
         <v>41</v>
       </c>
+      <c r="I6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J6" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -784,15 +791,15 @@
         <v>46</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" t="s">
         <v>47</v>
-      </c>
-      <c r="B10" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.3">
@@ -800,7 +807,13 @@
         <v>49</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>47</v>
+      </c>
+      <c r="I11" t="s">
+        <v>74</v>
+      </c>
+      <c r="J11" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.3">
@@ -808,7 +821,7 @@
         <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.3">
@@ -816,13 +829,13 @@
         <v>51</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
-      </c>
-      <c r="I13" t="s">
-        <v>76</v>
-      </c>
-      <c r="J13" t="s">
-        <v>76</v>
+        <v>47</v>
+      </c>
+      <c r="M13" t="s">
+        <v>74</v>
+      </c>
+      <c r="N13" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.3">
@@ -830,7 +843,10 @@
         <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>47</v>
+      </c>
+      <c r="D14" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.3">
@@ -838,13 +854,16 @@
         <v>53</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M15" t="s">
-        <v>77</v>
-      </c>
-      <c r="N15" t="s">
-        <v>77</v>
+        <v>47</v>
+      </c>
+      <c r="D15" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.3">
@@ -852,201 +871,203 @@
         <v>54</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+      <c r="I16" t="s">
+        <v>77</v>
+      </c>
+      <c r="P16" t="s">
+        <v>77</v>
+      </c>
+      <c r="W16" t="s">
+        <v>77</v>
+      </c>
+      <c r="X16" t="s">
+        <v>77</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>55</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" t="s">
         <v>39</v>
       </c>
-      <c r="Z17" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>56</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" t="s">
         <v>57</v>
-      </c>
-      <c r="B19" t="s">
-        <v>48</v>
       </c>
       <c r="C19" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+      <c r="D21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>61</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+      <c r="D22" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>62</v>
       </c>
       <c r="B23" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D23" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>63</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" t="s">
+        <v>57</v>
+      </c>
+      <c r="E24" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" t="s">
         <v>64</v>
       </c>
-      <c r="B25" t="s">
-        <v>59</v>
-      </c>
-      <c r="D25" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
-      </c>
-      <c r="E26" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>74</v>
+      </c>
+      <c r="R26" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>67</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>68</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>76</v>
-      </c>
-      <c r="R28" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>69</v>
       </c>
       <c r="B29" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>70</v>
       </c>
       <c r="B30" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+      <c r="H30" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>71</v>
       </c>
       <c r="B31" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+      <c r="H31" t="s">
+        <v>78</v>
+      </c>
+      <c r="I31" t="s">
+        <v>76</v>
+      </c>
+      <c r="O31" t="s">
+        <v>74</v>
+      </c>
+      <c r="P31" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>72</v>
       </c>
       <c r="B32" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+      <c r="H32" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>73</v>
       </c>
       <c r="B33" t="s">
-        <v>66</v>
-      </c>
-      <c r="I33" t="s">
-        <v>79</v>
-      </c>
-      <c r="P33" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>74</v>
-      </c>
-      <c r="B34" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>75</v>
-      </c>
-      <c r="B35" t="s">
-        <v>66</v>
+        <v>64</v>
+      </c>
+      <c r="H33" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
